--- a/research/traditional_assets/database/data/australia/australia_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_telecom_wireless.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.5660000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,16 +597,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-15.24390243902439</v>
+        <v>-14.66666666666667</v>
       </c>
       <c r="J2">
-        <v>-15.24390243902439</v>
+        <v>-14.66666666666667</v>
       </c>
       <c r="K2">
-        <v>64.3</v>
+        <v>-2.24</v>
       </c>
       <c r="L2">
-        <v>784.1463414634146</v>
+        <v>-29.86666666666667</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,61 +624,61 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.4</v>
+        <v>3.17</v>
       </c>
       <c r="V2">
-        <v>0.02398041036899434</v>
+        <v>0.005769930833636695</v>
       </c>
       <c r="W2">
-        <v>0.1392377652663491</v>
+        <v>-0.003954802259887006</v>
       </c>
       <c r="X2">
-        <v>0.04494424121313129</v>
+        <v>0.07517196499144081</v>
       </c>
       <c r="Y2">
-        <v>0.09429352405321778</v>
+        <v>-0.07912676725132782</v>
       </c>
       <c r="Z2">
-        <v>0.0001468481375358166</v>
+        <v>0.0001241721854304636</v>
       </c>
       <c r="AA2">
-        <v>-0.002238538681948424</v>
+        <v>-0.001821192052980133</v>
       </c>
       <c r="AB2">
-        <v>0.04343441995941898</v>
+        <v>0.07425630458076087</v>
       </c>
       <c r="AC2">
-        <v>-0.0456729586413674</v>
+        <v>-0.076077496633741</v>
       </c>
       <c r="AD2">
-        <v>66</v>
+        <v>15.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>66</v>
+        <v>15.2</v>
       </c>
       <c r="AG2">
-        <v>37.6</v>
+        <v>12.03</v>
       </c>
       <c r="AH2">
-        <v>0.05278733104055027</v>
+        <v>0.02692171448813319</v>
       </c>
       <c r="AI2">
-        <v>0.1043643263757116</v>
+        <v>0.02858217374952989</v>
       </c>
       <c r="AJ2">
-        <v>0.03077174891562321</v>
+        <v>0.02142742639331707</v>
       </c>
       <c r="AK2">
-        <v>0.06225165562913908</v>
+        <v>0.02275693774473639</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.5660000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-15.24390243902439</v>
+        <v>-14.66666666666667</v>
       </c>
       <c r="J3">
-        <v>-15.24390243902439</v>
+        <v>-14.66666666666667</v>
       </c>
       <c r="K3">
-        <v>64.3</v>
+        <v>-2.24</v>
       </c>
       <c r="L3">
-        <v>784.1463414634146</v>
+        <v>-29.86666666666667</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -731,7 +731,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,61 +740,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28.4</v>
+        <v>3.17</v>
       </c>
       <c r="V3">
-        <v>0.02398041036899434</v>
+        <v>0.005769930833636695</v>
       </c>
       <c r="W3">
-        <v>0.1392377652663491</v>
+        <v>-0.003954802259887006</v>
       </c>
       <c r="X3">
-        <v>0.04494424121313129</v>
+        <v>0.07517196499144081</v>
       </c>
       <c r="Y3">
-        <v>0.09429352405321778</v>
+        <v>-0.07912676725132782</v>
       </c>
       <c r="Z3">
-        <v>0.0001468481375358166</v>
+        <v>0.0001241721854304636</v>
       </c>
       <c r="AA3">
-        <v>-0.002238538681948424</v>
+        <v>-0.001821192052980133</v>
       </c>
       <c r="AB3">
-        <v>0.04343441995941898</v>
+        <v>0.07425630458076087</v>
       </c>
       <c r="AC3">
-        <v>-0.0456729586413674</v>
+        <v>-0.076077496633741</v>
       </c>
       <c r="AD3">
-        <v>66</v>
+        <v>15.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>66</v>
+        <v>15.2</v>
       </c>
       <c r="AG3">
-        <v>37.6</v>
+        <v>12.03</v>
       </c>
       <c r="AH3">
-        <v>0.05278733104055027</v>
+        <v>0.02692171448813319</v>
       </c>
       <c r="AI3">
-        <v>0.1043643263757116</v>
+        <v>0.02858217374952989</v>
       </c>
       <c r="AJ3">
-        <v>0.03077174891562321</v>
+        <v>0.02142742639331707</v>
       </c>
       <c r="AK3">
-        <v>0.06225165562913908</v>
+        <v>0.02275693774473639</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/australia/australia_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_telecom_wireless.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.5</v>
+        <v>-0.474</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,16 +597,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-14.66666666666667</v>
+        <v>-2.352941176470588</v>
       </c>
       <c r="J2">
-        <v>-14.66666666666667</v>
+        <v>-2.352941176470588</v>
       </c>
       <c r="K2">
-        <v>-2.24</v>
+        <v>-304.4</v>
       </c>
       <c r="L2">
-        <v>-29.86666666666667</v>
+        <v>-1119.117647058823</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.17</v>
+        <v>12.4</v>
       </c>
       <c r="V2">
-        <v>0.005769930833636695</v>
+        <v>0.04043038800130421</v>
       </c>
       <c r="W2">
-        <v>-0.003954802259887006</v>
+        <v>-0.589237320944638</v>
       </c>
       <c r="X2">
-        <v>0.07517196499144081</v>
+        <v>0.06806714487792773</v>
       </c>
       <c r="Y2">
-        <v>-0.07912676725132782</v>
+        <v>-0.6573044658225657</v>
       </c>
       <c r="Z2">
-        <v>0.0001241721854304636</v>
+        <v>0.000514537578268354</v>
       </c>
       <c r="AA2">
-        <v>-0.001821192052980133</v>
+        <v>-0.001210676654749068</v>
       </c>
       <c r="AB2">
-        <v>0.07425630458076087</v>
+        <v>0.06806714487792773</v>
       </c>
       <c r="AC2">
-        <v>-0.076077496633741</v>
+        <v>-0.06927782153267679</v>
       </c>
       <c r="AD2">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>12.03</v>
+        <v>-12.4</v>
       </c>
       <c r="AH2">
-        <v>0.02692171448813319</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.02858217374952989</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.02142742639331707</v>
+        <v>-0.04213387699626232</v>
       </c>
       <c r="AK2">
-        <v>0.02275693774473639</v>
+        <v>-0.06735469853340577</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>-0.474</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-14.66666666666667</v>
+        <v>-2.352941176470588</v>
       </c>
       <c r="J3">
-        <v>-14.66666666666667</v>
+        <v>-2.352941176470588</v>
       </c>
       <c r="K3">
-        <v>-2.24</v>
+        <v>-304.4</v>
       </c>
       <c r="L3">
-        <v>-29.86666666666667</v>
+        <v>-1119.117647058823</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.17</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.005769930833636695</v>
+        <v>0.04043038800130421</v>
       </c>
       <c r="W3">
-        <v>-0.003954802259887006</v>
+        <v>-0.589237320944638</v>
       </c>
       <c r="X3">
-        <v>0.07517196499144081</v>
+        <v>0.06806714487792773</v>
       </c>
       <c r="Y3">
-        <v>-0.07912676725132782</v>
+        <v>-0.6573044658225657</v>
       </c>
       <c r="Z3">
-        <v>0.0001241721854304636</v>
+        <v>0.000514537578268354</v>
       </c>
       <c r="AA3">
-        <v>-0.001821192052980133</v>
+        <v>-0.001210676654749068</v>
       </c>
       <c r="AB3">
-        <v>0.07425630458076087</v>
+        <v>0.06806714487792773</v>
       </c>
       <c r="AC3">
-        <v>-0.076077496633741</v>
+        <v>-0.06927782153267679</v>
       </c>
       <c r="AD3">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>12.03</v>
+        <v>-12.4</v>
       </c>
       <c r="AH3">
-        <v>0.02692171448813319</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.02858217374952989</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.02142742639331707</v>
+        <v>-0.04213387699626232</v>
       </c>
       <c r="AK3">
-        <v>0.02275693774473639</v>
+        <v>-0.06735469853340577</v>
       </c>
       <c r="AL3">
         <v>0</v>
